--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/136.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/136.xlsx
@@ -426,13 +426,13 @@
         <v>-20.17966110024386</v>
       </c>
       <c r="E2">
-        <v>-21.47024907375804</v>
+        <v>-23.16665619329742</v>
       </c>
       <c r="F2">
-        <v>-3.778742755591794</v>
+        <v>-4.039062831736238</v>
       </c>
       <c r="G2">
-        <v>-13.18664559578627</v>
+        <v>-16.62048247203099</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.85145231903698</v>
       </c>
       <c r="E3">
-        <v>-22.11317464252303</v>
+        <v>-22.35300715444326</v>
       </c>
       <c r="F3">
-        <v>-3.652996505905902</v>
+        <v>-4.538172502104726</v>
       </c>
       <c r="G3">
-        <v>-14.27136570500171</v>
+        <v>-15.95395875170014</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.39221945077371</v>
       </c>
       <c r="E4">
-        <v>-23.28428330564666</v>
+        <v>-23.6225965418117</v>
       </c>
       <c r="F4">
-        <v>-3.762568367077411</v>
+        <v>-4.097990945143824</v>
       </c>
       <c r="G4">
-        <v>-12.86636686758948</v>
+        <v>-16.66613655029031</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.8309197841155</v>
       </c>
       <c r="E5">
-        <v>-22.99085177537165</v>
+        <v>-23.83146787694149</v>
       </c>
       <c r="F5">
-        <v>-3.45231800268395</v>
+        <v>-4.705453023128933</v>
       </c>
       <c r="G5">
-        <v>-13.9649995444337</v>
+        <v>-16.21241469722381</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.14508939496196</v>
       </c>
       <c r="E6">
-        <v>-23.39863633128835</v>
+        <v>-24.86231158615154</v>
       </c>
       <c r="F6">
-        <v>-3.493485646102841</v>
+        <v>-4.598321652773116</v>
       </c>
       <c r="G6">
-        <v>-13.26003707984637</v>
+        <v>-15.49162616968599</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.35139684210078</v>
       </c>
       <c r="E7">
-        <v>-23.94344798220316</v>
+        <v>-23.54860127652637</v>
       </c>
       <c r="F7">
-        <v>-3.435618615658599</v>
+        <v>-3.894497404657179</v>
       </c>
       <c r="G7">
-        <v>-12.82866306444272</v>
+        <v>-15.27944999552856</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.45051820948544</v>
       </c>
       <c r="E8">
-        <v>-24.34895924416802</v>
+        <v>-26.94238008056877</v>
       </c>
       <c r="F8">
-        <v>-3.428486396068417</v>
+        <v>-4.217861645883436</v>
       </c>
       <c r="G8">
-        <v>-13.40367502970427</v>
+        <v>-13.01201100804417</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.46241521818402</v>
       </c>
       <c r="E9">
-        <v>-26.49096820606217</v>
+        <v>-26.61598125951791</v>
       </c>
       <c r="F9">
-        <v>-3.393543508750161</v>
+        <v>-3.983338555395585</v>
       </c>
       <c r="G9">
-        <v>-12.67704669983518</v>
+        <v>-14.8894246939104</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.41433315745976</v>
       </c>
       <c r="E10">
-        <v>-25.98626072095929</v>
+        <v>-25.069222092036</v>
       </c>
       <c r="F10">
-        <v>-3.449666878981504</v>
+        <v>-3.550584579178095</v>
       </c>
       <c r="G10">
-        <v>-12.68932551324033</v>
+        <v>-12.82125737407137</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.33842414073785</v>
       </c>
       <c r="E11">
-        <v>-26.03318476862677</v>
+        <v>-27.2694128879807</v>
       </c>
       <c r="F11">
-        <v>-2.989084022417912</v>
+        <v>-4.162245061545033</v>
       </c>
       <c r="G11">
-        <v>-11.59252191280655</v>
+        <v>-15.00736122347417</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.2895700459107</v>
       </c>
       <c r="E12">
-        <v>-26.74133394852424</v>
+        <v>-27.09024381386722</v>
       </c>
       <c r="F12">
-        <v>-2.95230245253183</v>
+        <v>-3.724765306875871</v>
       </c>
       <c r="G12">
-        <v>-11.80678704119926</v>
+        <v>-13.01076624292141</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.30767686946828</v>
       </c>
       <c r="E13">
-        <v>-29.13859034786072</v>
+        <v>-29.14080024317647</v>
       </c>
       <c r="F13">
-        <v>-2.92361203616773</v>
+        <v>-4.68086440508582</v>
       </c>
       <c r="G13">
-        <v>-11.28937194722995</v>
+        <v>-13.47988378801829</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.45731230430995</v>
       </c>
       <c r="E14">
-        <v>-26.94921807632035</v>
+        <v>-27.51472485345021</v>
       </c>
       <c r="F14">
-        <v>-2.980596942417072</v>
+        <v>-3.472169756333984</v>
       </c>
       <c r="G14">
-        <v>-11.25860373698796</v>
+        <v>-13.55537581322306</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.77327201864604</v>
       </c>
       <c r="E15">
-        <v>-28.04396308225264</v>
+        <v>-32.51454507820894</v>
       </c>
       <c r="F15">
-        <v>-2.696421504068363</v>
+        <v>-4.009097532110208</v>
       </c>
       <c r="G15">
-        <v>-11.02584259066735</v>
+        <v>-12.34735940121578</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.283094294176859</v>
       </c>
       <c r="E16">
-        <v>-29.38963536142395</v>
+        <v>-31.4861852369921</v>
       </c>
       <c r="F16">
-        <v>-2.464320691778178</v>
+        <v>-3.039790326565494</v>
       </c>
       <c r="G16">
-        <v>-10.11939204819612</v>
+        <v>-11.91312176392065</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.99491069397239</v>
       </c>
       <c r="E17">
-        <v>-28.64451119125385</v>
+        <v>-30.84415857031762</v>
       </c>
       <c r="F17">
-        <v>-2.263599428496509</v>
+        <v>-2.573255111318722</v>
       </c>
       <c r="G17">
-        <v>-10.01461328187819</v>
+        <v>-11.44045862455121</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.893161292139112</v>
       </c>
       <c r="E18">
-        <v>-30.31974769480738</v>
+        <v>-31.62992353046956</v>
       </c>
       <c r="F18">
-        <v>-2.050496752367934</v>
+        <v>-3.066413214856989</v>
       </c>
       <c r="G18">
-        <v>-10.44469949506706</v>
+        <v>-12.42257830641356</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.957867298535282</v>
       </c>
       <c r="E19">
-        <v>-31.88318296782253</v>
+        <v>-32.94898649637179</v>
       </c>
       <c r="F19">
-        <v>-1.986107229110955</v>
+        <v>-2.87855797843235</v>
       </c>
       <c r="G19">
-        <v>-8.567110350287255</v>
+        <v>-11.79877552099423</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.146844923386517</v>
       </c>
       <c r="E20">
-        <v>-31.86390298973487</v>
+        <v>-32.70203522331151</v>
       </c>
       <c r="F20">
-        <v>-1.850373338069344</v>
+        <v>-2.735813813156046</v>
       </c>
       <c r="G20">
-        <v>-9.385622871598819</v>
+        <v>-11.67653693750218</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.427874827723025</v>
       </c>
       <c r="E21">
-        <v>-30.96463862129169</v>
+        <v>-33.22542492793303</v>
       </c>
       <c r="F21">
-        <v>-1.887869159323289</v>
+        <v>-2.966049811730803</v>
       </c>
       <c r="G21">
-        <v>-9.342602332315991</v>
+        <v>-11.00411216974757</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.75532911192389</v>
       </c>
       <c r="E22">
-        <v>-32.58751464413153</v>
+        <v>-35.61919213804661</v>
       </c>
       <c r="F22">
-        <v>-1.259607479697756</v>
+        <v>-2.528466324324179</v>
       </c>
       <c r="G22">
-        <v>-10.1353819831508</v>
+        <v>-9.701220488403081</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.09172394790807</v>
       </c>
       <c r="E23">
-        <v>-32.03350566250715</v>
+        <v>-32.98686265297195</v>
       </c>
       <c r="F23">
-        <v>-1.330884539980981</v>
+        <v>-2.067871589966221</v>
       </c>
       <c r="G23">
-        <v>-9.503183654243879</v>
+        <v>-10.67364689292644</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.40192810358432</v>
       </c>
       <c r="E24">
-        <v>-33.97603081588941</v>
+        <v>-33.96960038279852</v>
       </c>
       <c r="F24">
-        <v>-1.395299402532608</v>
+        <v>-2.442222451287093</v>
       </c>
       <c r="G24">
-        <v>-9.856107672003423</v>
+        <v>-10.22110193879915</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.65066983631903</v>
       </c>
       <c r="E25">
-        <v>-33.53087955669841</v>
+        <v>-33.84191326544124</v>
       </c>
       <c r="F25">
-        <v>-1.166403219162313</v>
+        <v>-2.122858651203236</v>
       </c>
       <c r="G25">
-        <v>-9.578578018355241</v>
+        <v>-11.25034392586748</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.8168029861634</v>
       </c>
       <c r="E26">
-        <v>-33.16656155854432</v>
+        <v>-35.54997214860236</v>
       </c>
       <c r="F26">
-        <v>-1.292095622847081</v>
+        <v>-2.490622879621796</v>
       </c>
       <c r="G26">
-        <v>-9.327463207564904</v>
+        <v>-10.37429081253785</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.88075997207024</v>
       </c>
       <c r="E27">
-        <v>-34.00145140473147</v>
+        <v>-33.90021736829</v>
       </c>
       <c r="F27">
-        <v>-1.290743137995295</v>
+        <v>-1.894423326254335</v>
       </c>
       <c r="G27">
-        <v>-9.661993834308257</v>
+        <v>-11.19482938771944</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.84167021979487</v>
       </c>
       <c r="E28">
-        <v>-34.58244556296756</v>
+        <v>-33.62090109149689</v>
       </c>
       <c r="F28">
-        <v>-1.334092336312704</v>
+        <v>-2.399800512783175</v>
       </c>
       <c r="G28">
-        <v>-9.255640922090414</v>
+        <v>-10.08535632950687</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.70192932274649</v>
       </c>
       <c r="E29">
-        <v>-33.79304650242447</v>
+        <v>-34.1565652249162</v>
       </c>
       <c r="F29">
-        <v>-1.57992387888975</v>
+        <v>-2.690184870173363</v>
       </c>
       <c r="G29">
-        <v>-9.42450522895756</v>
+        <v>-10.40436711876212</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.47897806212344</v>
       </c>
       <c r="E30">
-        <v>-34.08844112618181</v>
+        <v>-33.71669416641814</v>
       </c>
       <c r="F30">
-        <v>-1.385422620590969</v>
+        <v>-2.381947395998425</v>
       </c>
       <c r="G30">
-        <v>-9.766580588984912</v>
+        <v>-9.962647648548248</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.19431204663085</v>
       </c>
       <c r="E31">
-        <v>-33.29285164167024</v>
+        <v>-35.42192048908747</v>
       </c>
       <c r="F31">
-        <v>-1.179848090531437</v>
+        <v>-1.706259267176185</v>
       </c>
       <c r="G31">
-        <v>-10.09917785713333</v>
+        <v>-11.50796395864249</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.869783883219808</v>
       </c>
       <c r="E32">
-        <v>-33.24026020878216</v>
+        <v>-33.99215218335672</v>
       </c>
       <c r="F32">
-        <v>-1.300611209554398</v>
+        <v>-2.559120536023425</v>
       </c>
       <c r="G32">
-        <v>-10.06932666800572</v>
+        <v>-11.09079549414785</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.532922117594756</v>
       </c>
       <c r="E33">
-        <v>-31.74777480228218</v>
+        <v>-35.52868379229231</v>
       </c>
       <c r="F33">
-        <v>-1.078666703299926</v>
+        <v>-2.074594421577261</v>
       </c>
       <c r="G33">
-        <v>-9.829550475687389</v>
+        <v>-11.24006799251359</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.20162982463229</v>
       </c>
       <c r="E34">
-        <v>-32.13838059205079</v>
+        <v>-33.46365209581754</v>
       </c>
       <c r="F34">
-        <v>-1.453274916832057</v>
+        <v>-2.54114468203023</v>
       </c>
       <c r="G34">
-        <v>-10.21680485068918</v>
+        <v>-11.2649798476966</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.898868322882144</v>
       </c>
       <c r="E35">
-        <v>-31.61802949348841</v>
+        <v>-32.3395920133966</v>
       </c>
       <c r="F35">
-        <v>-0.9923246404960824</v>
+        <v>-2.452890294333493</v>
       </c>
       <c r="G35">
-        <v>-9.31403232431208</v>
+        <v>-10.64817555554729</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.634723923159854</v>
       </c>
       <c r="E36">
-        <v>-31.94689633287345</v>
+        <v>-32.86720904850428</v>
       </c>
       <c r="F36">
-        <v>-1.334182607549884</v>
+        <v>-2.567172096897519</v>
       </c>
       <c r="G36">
-        <v>-9.772215137492752</v>
+        <v>-11.99960645558857</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.424362168771991</v>
       </c>
       <c r="E37">
-        <v>-30.28320290956547</v>
+        <v>-33.82000903666614</v>
       </c>
       <c r="F37">
-        <v>-1.556852451113628</v>
+        <v>-2.040272346977857</v>
       </c>
       <c r="G37">
-        <v>-9.52979712983408</v>
+        <v>-11.15766189295005</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.268965530284184</v>
       </c>
       <c r="E38">
-        <v>-30.79626995768651</v>
+        <v>-34.51378936853727</v>
       </c>
       <c r="F38">
-        <v>-1.528638730230074</v>
+        <v>-1.683879127032153</v>
       </c>
       <c r="G38">
-        <v>-9.695579318804164</v>
+        <v>-11.13564676511389</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.167069284452992</v>
       </c>
       <c r="E39">
-        <v>-30.64622123567936</v>
+        <v>-32.27420084872584</v>
       </c>
       <c r="F39">
-        <v>-1.385885854571235</v>
+        <v>-1.436992044462466</v>
       </c>
       <c r="G39">
-        <v>-9.453896252255209</v>
+        <v>-11.7479321626021</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.116009750745185</v>
       </c>
       <c r="E40">
-        <v>-30.96782213851909</v>
+        <v>-33.57927762265539</v>
       </c>
       <c r="F40">
-        <v>-1.108695351162573</v>
+        <v>-1.732478310459243</v>
       </c>
       <c r="G40">
-        <v>-9.948289812544429</v>
+        <v>-12.57513486595425</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.105541196708995</v>
       </c>
       <c r="E41">
-        <v>-29.88523155682339</v>
+        <v>-30.29596414931909</v>
       </c>
       <c r="F41">
-        <v>-1.068911074860819</v>
+        <v>-2.289125600441562</v>
       </c>
       <c r="G41">
-        <v>-10.83134141914409</v>
+        <v>-11.49563548705424</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.132391260743361</v>
       </c>
       <c r="E42">
-        <v>-29.68755913791457</v>
+        <v>-31.45594182333187</v>
       </c>
       <c r="F42">
-        <v>-1.230801452801828</v>
+        <v>-1.802755260456869</v>
       </c>
       <c r="G42">
-        <v>-8.962962212054528</v>
+        <v>-10.81448412125812</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.185515655433743</v>
       </c>
       <c r="E43">
-        <v>-28.73183828401777</v>
+        <v>-32.08317622966028</v>
       </c>
       <c r="F43">
-        <v>-1.203597344439366</v>
+        <v>-1.730234199177065</v>
       </c>
       <c r="G43">
-        <v>-10.53103852273126</v>
+        <v>-9.225779801326189</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.263559745730728</v>
       </c>
       <c r="E44">
-        <v>-27.48093790887898</v>
+        <v>-31.92090968478043</v>
       </c>
       <c r="F44">
-        <v>-0.9270727893681463</v>
+        <v>-1.758055952846548</v>
       </c>
       <c r="G44">
-        <v>-9.557417011268219</v>
+        <v>-10.46259630425237</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.361118169598242</v>
       </c>
       <c r="E45">
-        <v>-28.38008906547197</v>
+        <v>-29.82279295720563</v>
       </c>
       <c r="F45">
-        <v>-0.9330639488462537</v>
+        <v>-1.767206605625957</v>
       </c>
       <c r="G45">
-        <v>-9.613153355967389</v>
+        <v>-11.85654454065451</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.477173524150039</v>
       </c>
       <c r="E46">
-        <v>-26.73051995259392</v>
+        <v>-28.25397106435835</v>
       </c>
       <c r="F46">
-        <v>-1.309805414246482</v>
+        <v>-2.174766196287679</v>
       </c>
       <c r="G46">
-        <v>-9.149001629179411</v>
+        <v>-12.62283982717515</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.617505775746325</v>
       </c>
       <c r="E47">
-        <v>-26.50845264420578</v>
+        <v>-28.58674597681201</v>
       </c>
       <c r="F47">
-        <v>-0.6174749118118464</v>
+        <v>-2.497456570646917</v>
       </c>
       <c r="G47">
-        <v>-9.20842261106379</v>
+        <v>-12.20467819901873</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.780738942331041</v>
       </c>
       <c r="E48">
-        <v>-26.7259643077422</v>
+        <v>-26.63318040379905</v>
       </c>
       <c r="F48">
-        <v>-1.085117929346468</v>
+        <v>-1.847937598371398</v>
       </c>
       <c r="G48">
-        <v>-9.319478171724182</v>
+        <v>-11.38052450810824</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.978706824974859</v>
       </c>
       <c r="E49">
-        <v>-26.16451051484921</v>
+        <v>-27.44825591196562</v>
       </c>
       <c r="F49">
-        <v>-1.127117018370965</v>
+        <v>-1.737178749616267</v>
       </c>
       <c r="G49">
-        <v>-9.590870073942554</v>
+        <v>-10.9887048908078</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.21373906605003</v>
       </c>
       <c r="E50">
-        <v>-25.94978386282751</v>
+        <v>-25.97354476594575</v>
       </c>
       <c r="F50">
-        <v>-1.115472028774738</v>
+        <v>-2.311980852360226</v>
       </c>
       <c r="G50">
-        <v>-10.19391242828512</v>
+        <v>-10.69105043082639</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.494898257707398</v>
       </c>
       <c r="E51">
-        <v>-25.18213959141726</v>
+        <v>-25.97291530805868</v>
       </c>
       <c r="F51">
-        <v>-1.204199152687233</v>
+        <v>-1.845713283413164</v>
       </c>
       <c r="G51">
-        <v>-10.26981661640952</v>
+        <v>-11.06168586722104</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.822704227962141</v>
       </c>
       <c r="E52">
-        <v>-24.69995220755453</v>
+        <v>-25.98947593750474</v>
       </c>
       <c r="F52">
-        <v>-1.413198446788904</v>
+        <v>-1.782123531643481</v>
       </c>
       <c r="G52">
-        <v>-9.460626591336547</v>
+        <v>-11.78307029295592</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.19507231792475</v>
       </c>
       <c r="E53">
-        <v>-25.64896639144598</v>
+        <v>-26.75765004037387</v>
       </c>
       <c r="F53">
-        <v>-1.098740175778121</v>
+        <v>-1.937996618958778</v>
       </c>
       <c r="G53">
-        <v>-9.679718495125515</v>
+        <v>-10.33852367853156</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.6105705405959</v>
       </c>
       <c r="E54">
-        <v>-24.73481692893959</v>
+        <v>-26.98655534451359</v>
       </c>
       <c r="F54">
-        <v>-1.347712999038441</v>
+        <v>-2.272773045011692</v>
       </c>
       <c r="G54">
-        <v>-9.839975383590554</v>
+        <v>-9.780236589334406</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.05173211866825</v>
       </c>
       <c r="E55">
-        <v>-23.65048741322494</v>
+        <v>-25.41524279096209</v>
       </c>
       <c r="F55">
-        <v>-1.140358383529954</v>
+        <v>-2.368192118269876</v>
       </c>
       <c r="G55">
-        <v>-9.416606267300859</v>
+        <v>-10.94094365031274</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.51629260204835</v>
       </c>
       <c r="E56">
-        <v>-22.17629251324194</v>
+        <v>-24.86623777311619</v>
       </c>
       <c r="F56">
-        <v>-1.458671394738917</v>
+        <v>-2.152477119233784</v>
       </c>
       <c r="G56">
-        <v>-9.374631860408439</v>
+        <v>-11.63573115318512</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.98552797175135</v>
       </c>
       <c r="E57">
-        <v>-23.39610491431807</v>
+        <v>-23.64908358628256</v>
       </c>
       <c r="F57">
-        <v>-1.082559452440076</v>
+        <v>-2.811453983236308</v>
       </c>
       <c r="G57">
-        <v>-9.71117529883967</v>
+        <v>-11.72655597005503</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.45283164119313</v>
       </c>
       <c r="E58">
-        <v>-22.22118327607998</v>
+        <v>-23.37322253515731</v>
       </c>
       <c r="F58">
-        <v>-1.417578185498052</v>
+        <v>-1.645304010196836</v>
       </c>
       <c r="G58">
-        <v>-10.36401818972949</v>
+        <v>-12.10338212660811</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.90530974797741</v>
       </c>
       <c r="E59">
-        <v>-23.06232920910871</v>
+        <v>-25.43823838197304</v>
       </c>
       <c r="F59">
-        <v>-1.153072374619102</v>
+        <v>-2.487605919852883</v>
       </c>
       <c r="G59">
-        <v>-10.23331785183906</v>
+        <v>-11.26041129485241</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.33615456678703</v>
       </c>
       <c r="E60">
-        <v>-22.99816978936804</v>
+        <v>-23.80096860449983</v>
       </c>
       <c r="F60">
-        <v>-0.9292765161494803</v>
+        <v>-1.973642671703489</v>
       </c>
       <c r="G60">
-        <v>-10.50320014529153</v>
+        <v>-11.05929565334168</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.74102258466074</v>
       </c>
       <c r="E61">
-        <v>-22.31886246042543</v>
+        <v>-23.6502836318946</v>
       </c>
       <c r="F61">
-        <v>-1.259694583523105</v>
+        <v>-2.437310587390358</v>
       </c>
       <c r="G61">
-        <v>-10.35722163973736</v>
+        <v>-11.26641993500618</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.10940988115044</v>
       </c>
       <c r="E62">
-        <v>-22.69862029070866</v>
+        <v>-23.08852643124309</v>
       </c>
       <c r="F62">
-        <v>-1.080229821038464</v>
+        <v>-2.863030533784424</v>
       </c>
       <c r="G62">
-        <v>-10.15273255232212</v>
+        <v>-12.77760783113608</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.44370465513801</v>
       </c>
       <c r="E63">
-        <v>-22.48323248148184</v>
+        <v>-21.92078242430716</v>
       </c>
       <c r="F63">
-        <v>-1.468261525909861</v>
+        <v>-2.283238173700916</v>
       </c>
       <c r="G63">
-        <v>-10.33039628923265</v>
+        <v>-13.43201661006597</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.73196069790897</v>
       </c>
       <c r="E64">
-        <v>-21.57585761609092</v>
+        <v>-24.36515759569345</v>
       </c>
       <c r="F64">
-        <v>-1.007395185987404</v>
+        <v>-1.771727294161579</v>
       </c>
       <c r="G64">
-        <v>-10.75148443964579</v>
+        <v>-13.07654678278673</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.97670339738667</v>
       </c>
       <c r="E65">
-        <v>-20.52876121366734</v>
+        <v>-24.67887668952283</v>
       </c>
       <c r="F65">
-        <v>-1.189752587326595</v>
+        <v>-2.140239823625184</v>
       </c>
       <c r="G65">
-        <v>-10.98657621002605</v>
+        <v>-12.32911829529439</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.17032620024609</v>
       </c>
       <c r="E66">
-        <v>-20.76664195329026</v>
+        <v>-23.32322365363862</v>
       </c>
       <c r="F66">
-        <v>-1.45478102115764</v>
+        <v>-2.724799138514165</v>
       </c>
       <c r="G66">
-        <v>-10.62233343706774</v>
+        <v>-12.33942402355814</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.31637419280985</v>
       </c>
       <c r="E67">
-        <v>-21.03808321378403</v>
+        <v>-21.64571385613324</v>
       </c>
       <c r="F67">
-        <v>-1.220916752330612</v>
+        <v>-2.570600028351488</v>
       </c>
       <c r="G67">
-        <v>-11.17441325337876</v>
+        <v>-11.44058111473616</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.41312340985593</v>
       </c>
       <c r="E68">
-        <v>-21.56684142434165</v>
+        <v>-23.64010815079936</v>
       </c>
       <c r="F68">
-        <v>-1.577703523196303</v>
+        <v>-2.216094585856987</v>
       </c>
       <c r="G68">
-        <v>-10.56547481743076</v>
+        <v>-10.81777480352415</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.46321338539555</v>
       </c>
       <c r="E69">
-        <v>-21.36692288232502</v>
+        <v>-24.52585502432964</v>
       </c>
       <c r="F69">
-        <v>-1.35172769353408</v>
+        <v>-1.806647217744061</v>
       </c>
       <c r="G69">
-        <v>-10.80334082497293</v>
+        <v>-12.03686002454199</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.47144527857771</v>
       </c>
       <c r="E70">
-        <v>-21.13347551875561</v>
+        <v>-22.6313362239027</v>
       </c>
       <c r="F70">
-        <v>-1.823310971386315</v>
+        <v>-2.207062711021236</v>
       </c>
       <c r="G70">
-        <v>-11.74640269056296</v>
+        <v>-12.66152355180153</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.43458444666736</v>
       </c>
       <c r="E71">
-        <v>-21.35226874043621</v>
+        <v>-24.03051242347463</v>
       </c>
       <c r="F71">
-        <v>-1.857112798592497</v>
+        <v>-2.286160902967859</v>
       </c>
       <c r="G71">
-        <v>-10.42481304801266</v>
+        <v>-11.78610937376098</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.36267359259634</v>
       </c>
       <c r="E72">
-        <v>-21.35105510940215</v>
+        <v>-20.96519289615657</v>
       </c>
       <c r="F72">
-        <v>-1.401865447258019</v>
+        <v>-2.206738051308571</v>
       </c>
       <c r="G72">
-        <v>-9.296208347128644</v>
+        <v>-11.92629773516695</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.25392778098191</v>
       </c>
       <c r="E73">
-        <v>-21.94937973766559</v>
+        <v>-22.26138706832008</v>
       </c>
       <c r="F73">
-        <v>-1.547963109810266</v>
+        <v>-2.592017275298933</v>
       </c>
       <c r="G73">
-        <v>-9.246007234571136</v>
+        <v>-11.95980045602438</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.11930249041877</v>
       </c>
       <c r="E74">
-        <v>-21.33936711798835</v>
+        <v>-22.35611821608653</v>
       </c>
       <c r="F74">
-        <v>-2.124295864321497</v>
+        <v>-2.878729018671218</v>
       </c>
       <c r="G74">
-        <v>-10.70076357143861</v>
+        <v>-12.09231497287032</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.95677231414345</v>
       </c>
       <c r="E75">
-        <v>-21.75103710460364</v>
+        <v>-24.57526520422734</v>
       </c>
       <c r="F75">
-        <v>-1.993525307618873</v>
+        <v>-2.703500669510378</v>
       </c>
       <c r="G75">
-        <v>-10.06787995960506</v>
+        <v>-10.76056857660555</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.77793617975232</v>
       </c>
       <c r="E76">
-        <v>-21.16554164320392</v>
+        <v>-22.97332658096196</v>
       </c>
       <c r="F76">
-        <v>-1.505461986010575</v>
+        <v>-2.851372082687917</v>
       </c>
       <c r="G76">
-        <v>-9.699952549461541</v>
+        <v>-11.71771681346517</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.58484734439472</v>
       </c>
       <c r="E77">
-        <v>-22.76204156918608</v>
+        <v>-22.74066264339588</v>
       </c>
       <c r="F77">
-        <v>-1.992431758684263</v>
+        <v>-3.15881216093443</v>
       </c>
       <c r="G77">
-        <v>-9.627021231231396</v>
+        <v>-12.29479786968877</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.38117010257175</v>
       </c>
       <c r="E78">
-        <v>-22.23986775983563</v>
+        <v>-23.94025993650176</v>
       </c>
       <c r="F78">
-        <v>-2.162627882298794</v>
+        <v>-2.790444540562088</v>
       </c>
       <c r="G78">
-        <v>-9.575505832094796</v>
+        <v>-9.884720717099343</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.17756976478315</v>
       </c>
       <c r="E79">
-        <v>-22.8389758141024</v>
+        <v>-26.22434071343855</v>
       </c>
       <c r="F79">
-        <v>-1.561615446654312</v>
+        <v>-2.495518906459377</v>
       </c>
       <c r="G79">
-        <v>-9.24225969702068</v>
+        <v>-9.727830653447743</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.97548810012038</v>
       </c>
       <c r="E80">
-        <v>-22.89852071882926</v>
+        <v>-22.22255087523029</v>
       </c>
       <c r="F80">
-        <v>-2.289689399747458</v>
+        <v>-3.546874748071178</v>
       </c>
       <c r="G80">
-        <v>-9.384844893397091</v>
+        <v>-11.07727522616546</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.7866308933246</v>
       </c>
       <c r="E81">
-        <v>-23.72562385396021</v>
+        <v>-25.15937495258071</v>
       </c>
       <c r="F81">
-        <v>-2.033180511888519</v>
+        <v>-2.732075475342652</v>
       </c>
       <c r="G81">
-        <v>-8.999189511890773</v>
+        <v>-12.11704474804868</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.60908135991518</v>
       </c>
       <c r="E82">
-        <v>-25.44486806792028</v>
+        <v>-26.43381433561136</v>
       </c>
       <c r="F82">
-        <v>-2.350035721802321</v>
+        <v>-3.055997972904101</v>
       </c>
       <c r="G82">
-        <v>-8.356695386356717</v>
+        <v>-9.780537848978479</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.45334366258105</v>
       </c>
       <c r="E83">
-        <v>-24.797644977322</v>
+        <v>-24.16598172341409</v>
       </c>
       <c r="F83">
-        <v>-2.389156425325506</v>
+        <v>-2.767669265792153</v>
       </c>
       <c r="G83">
-        <v>-8.872253264278497</v>
+        <v>-9.986291564789724</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.31746660499047</v>
       </c>
       <c r="E84">
-        <v>-25.75516816387386</v>
+        <v>-27.35187639966038</v>
       </c>
       <c r="F84">
-        <v>-2.696862566165813</v>
+        <v>-3.545367851892637</v>
       </c>
       <c r="G84">
-        <v>-8.954364725289041</v>
+        <v>-9.005684802238823</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.20573534229564</v>
       </c>
       <c r="E85">
-        <v>-26.25388447786459</v>
+        <v>-29.68961053664005</v>
       </c>
       <c r="F85">
-        <v>-2.410073221203672</v>
+        <v>-3.232525752768559</v>
       </c>
       <c r="G85">
-        <v>-9.335050977940913</v>
+        <v>-10.03847569412526</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.12130134579282</v>
       </c>
       <c r="E86">
-        <v>-27.92773526837177</v>
+        <v>-29.61051847385908</v>
       </c>
       <c r="F86">
-        <v>-2.253763822908672</v>
+        <v>-3.06071424912028</v>
       </c>
       <c r="G86">
-        <v>-8.54401267405976</v>
+        <v>-9.819367237608592</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.06027556317107</v>
       </c>
       <c r="E87">
-        <v>-29.01428826482418</v>
+        <v>-28.39786785442609</v>
       </c>
       <c r="F87">
-        <v>-2.569908740719399</v>
+        <v>-3.422524535149746</v>
       </c>
       <c r="G87">
-        <v>-7.782252834927919</v>
+        <v>-11.06465542656976</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.02744655875389</v>
       </c>
       <c r="E88">
-        <v>-29.75380165569877</v>
+        <v>-28.73964990168099</v>
       </c>
       <c r="F88">
-        <v>-2.782805535078966</v>
+        <v>-3.111365123560822</v>
       </c>
       <c r="G88">
-        <v>-8.537484278256317</v>
+        <v>-10.76005213150142</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.01454308734202</v>
       </c>
       <c r="E89">
-        <v>-30.7811493829749</v>
+        <v>-30.92589299768207</v>
       </c>
       <c r="F89">
-        <v>-2.904785732097943</v>
+        <v>-3.434338981278924</v>
       </c>
       <c r="G89">
-        <v>-8.227766190329801</v>
+        <v>-9.158906781432911</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.02293061176143</v>
       </c>
       <c r="E90">
-        <v>-30.21210133917104</v>
+        <v>-32.922540208167</v>
       </c>
       <c r="F90">
-        <v>-2.736216866311526</v>
+        <v>-3.873103121445507</v>
       </c>
       <c r="G90">
-        <v>-8.111887164818691</v>
+        <v>-9.517703706979121</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.03943326946295</v>
       </c>
       <c r="E91">
-        <v>-32.04338679279189</v>
+        <v>-33.21720574760911</v>
       </c>
       <c r="F91">
-        <v>-2.868824521876059</v>
+        <v>-4.086011001746482</v>
       </c>
       <c r="G91">
-        <v>-8.17507554752676</v>
+        <v>-9.584450926141908</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.0605822254329</v>
       </c>
       <c r="E92">
-        <v>-33.65334760776184</v>
+        <v>-33.26494039212396</v>
       </c>
       <c r="F92">
-        <v>-3.410568347341135</v>
+        <v>-4.557243488738448</v>
       </c>
       <c r="G92">
-        <v>-8.209107955670468</v>
+        <v>-9.776839969611114</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.07609069915915</v>
       </c>
       <c r="E93">
-        <v>-35.25557605336371</v>
+        <v>-37.4701039980167</v>
       </c>
       <c r="F93">
-        <v>-3.345933349667263</v>
+        <v>-4.533565501596713</v>
       </c>
       <c r="G93">
-        <v>-8.813014362398778</v>
+        <v>-9.898770672368011</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.07212654039599</v>
       </c>
       <c r="E94">
-        <v>-36.53656134557245</v>
+        <v>-36.83471154576346</v>
       </c>
       <c r="F94">
-        <v>-3.799865433238967</v>
+        <v>-4.318960680407343</v>
       </c>
       <c r="G94">
-        <v>-8.213941352157804</v>
+        <v>-10.60435386424396</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.04445944080985</v>
       </c>
       <c r="E95">
-        <v>-38.40340664133853</v>
+        <v>-39.83864760790755</v>
       </c>
       <c r="F95">
-        <v>-3.707431645631386</v>
+        <v>-4.008269253916433</v>
       </c>
       <c r="G95">
-        <v>-8.425597770665568</v>
+        <v>-10.60020906122879</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.9790268660487</v>
       </c>
       <c r="E96">
-        <v>-40.00399577934962</v>
+        <v>-41.24040503766386</v>
       </c>
       <c r="F96">
-        <v>-3.799056951369136</v>
+        <v>-4.290986099117021</v>
       </c>
       <c r="G96">
-        <v>-9.061937592042119</v>
+        <v>-11.05562425833863</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.87725607927943</v>
       </c>
       <c r="E97">
-        <v>-41.90065428374519</v>
+        <v>-43.62503831570396</v>
       </c>
       <c r="F97">
-        <v>-3.746021807672899</v>
+        <v>-5.134588231329644</v>
       </c>
       <c r="G97">
-        <v>-9.212746183538078</v>
+        <v>-9.887875666998269</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.72920691760307</v>
       </c>
       <c r="E98">
-        <v>-43.94331305438506</v>
+        <v>-45.63766424672496</v>
       </c>
       <c r="F98">
-        <v>-4.662638325557985</v>
+        <v>-4.637840658334034</v>
       </c>
       <c r="G98">
-        <v>-9.445974116779734</v>
+        <v>-11.35502337581924</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.54879622766139</v>
       </c>
       <c r="E99">
-        <v>-45.60726460071147</v>
+        <v>-46.58707467209207</v>
       </c>
       <c r="F99">
-        <v>-4.71379519403851</v>
+        <v>-4.686321855670425</v>
       </c>
       <c r="G99">
-        <v>-9.354136272974811</v>
+        <v>-10.57776025192699</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.33629999932362</v>
       </c>
       <c r="E100">
-        <v>-47.91868377523257</v>
+        <v>-47.01091493260298</v>
       </c>
       <c r="F100">
-        <v>-5.043452290719766</v>
+        <v>-4.829227558950103</v>
       </c>
       <c r="G100">
-        <v>-9.986387570610361</v>
+        <v>-11.31494591152082</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.11533707989124</v>
       </c>
       <c r="E101">
-        <v>-49.29563309225635</v>
+        <v>-51.26903338142291</v>
       </c>
       <c r="F101">
-        <v>-5.002465189775235</v>
+        <v>-5.318268027108227</v>
       </c>
       <c r="G101">
-        <v>-9.098661473709253</v>
+        <v>-12.05038360306992</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.88932192865492</v>
       </c>
       <c r="E102">
-        <v>-51.01555318096206</v>
+        <v>-51.79019168047715</v>
       </c>
       <c r="F102">
-        <v>-5.038831036858514</v>
+        <v>-5.162375935321945</v>
       </c>
       <c r="G102">
-        <v>-10.51050982984224</v>
+        <v>-11.97153302941555</v>
       </c>
     </row>
   </sheetData>
